--- a/red_book/excel/笔记列表明细表-20260921.xlsx
+++ b/red_book/excel/笔记列表明细表-20260921.xlsx
@@ -361,13 +361,13 @@
         <v>64464.0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4557.0</v>
+        <v>4623.0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.068</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>17.0</v>
@@ -455,7 +455,7 @@
         <v>11703.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2203.0</v>
+        <v>2223.0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.089</v>
@@ -467,7 +467,7 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>2.0</v>
@@ -502,7 +502,7 @@
         <v>10608.0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2082.0</v>
+        <v>2121.0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.198</v>
@@ -690,19 +690,19 @@
         <v>37049.0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6253.0</v>
+        <v>6385.0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>179.0</v>
+        <v>184.0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.0</v>
@@ -784,7 +784,7 @@
         <v>3154.0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.074</v>
@@ -831,7 +831,7 @@
         <v>30626.0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3197.0</v>
+        <v>3220.0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0.105</v>
@@ -878,7 +878,7 @@
         <v>2157.0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>191.0</v>
+        <v>196.0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0.089</v>
@@ -896,7 +896,7 @@
         <v>0.0</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>11.0</v>

--- a/red_book/excel/笔记列表明细表-20260921.xlsx
+++ b/red_book/excel/笔记列表明细表-20260921.xlsx
@@ -502,7 +502,7 @@
         <v>10608.0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2121.0</v>
+        <v>2122.0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.198</v>

--- a/red_book/excel/笔记列表明细表-20260921.xlsx
+++ b/red_book/excel/笔记列表明细表-20260921.xlsx
@@ -361,7 +361,7 @@
         <v>64464.0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4623.0</v>
+        <v>4633.0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.068</v>
@@ -408,7 +408,7 @@
         <v>2437.0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1329.0</v>
+        <v>1330.0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.046</v>
@@ -455,7 +455,7 @@
         <v>11703.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2223.0</v>
+        <v>2227.0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.089</v>
@@ -502,7 +502,7 @@
         <v>10608.0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2122.0</v>
+        <v>2128.0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.198</v>
@@ -690,7 +690,7 @@
         <v>37049.0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6385.0</v>
+        <v>6395.0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.17</v>
@@ -708,7 +708,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>55.0</v>
@@ -784,7 +784,7 @@
         <v>3154.0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.074</v>
@@ -831,7 +831,7 @@
         <v>30626.0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3220.0</v>
+        <v>3225.0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0.105</v>
@@ -878,7 +878,7 @@
         <v>2157.0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>196.0</v>
+        <v>198.0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0.089</v>

--- a/red_book/excel/笔记列表明细表-20260921.xlsx
+++ b/red_book/excel/笔记列表明细表-20260921.xlsx
@@ -361,13 +361,13 @@
         <v>64464.0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4633.0</v>
+        <v>4557.0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.068</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>51.0</v>
+        <v>50.0</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>17.0</v>
@@ -408,7 +408,7 @@
         <v>2437.0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1330.0</v>
+        <v>1329.0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.046</v>
@@ -455,7 +455,7 @@
         <v>11703.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2227.0</v>
+        <v>2203.0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.089</v>
@@ -467,7 +467,7 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>43.0</v>
+        <v>42.0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>2.0</v>
@@ -502,7 +502,7 @@
         <v>10608.0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2128.0</v>
+        <v>2082.0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.198</v>
@@ -690,25 +690,25 @@
         <v>37049.0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6395.0</v>
+        <v>6253.0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>184.0</v>
+        <v>179.0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>182.0</v>
+        <v>181.0</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>31.0</v>
+        <v>30.0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>55.0</v>
@@ -784,7 +784,7 @@
         <v>3154.0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>237.0</v>
+        <v>235.0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.074</v>
@@ -831,7 +831,7 @@
         <v>30626.0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3225.0</v>
+        <v>3197.0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0.105</v>
@@ -878,7 +878,7 @@
         <v>2157.0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>198.0</v>
+        <v>191.0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0.089</v>
@@ -896,7 +896,7 @@
         <v>0.0</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>11.0</v>
